--- a/Result/profitability/6204.xlsx
+++ b/Result/profitability/6204.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.26625</v>
       </c>
       <c r="N2" t="n">
-        <v>33.62375</v>
+        <v>33.32125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.315</v>
+        <v>0.31125</v>
       </c>
       <c r="N3" t="n">
-        <v>33.32875</v>
+        <v>33.11875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3575</v>
+        <v>0.3675</v>
       </c>
       <c r="N4" t="n">
-        <v>33.1825</v>
+        <v>33.295</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0.375</v>
+        <v>0.40125</v>
       </c>
       <c r="N5" t="n">
-        <v>32.94125</v>
+        <v>32.7</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39125</v>
+        <v>0.375</v>
       </c>
       <c r="N6" t="n">
-        <v>32.25625</v>
+        <v>31.81875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4075</v>
+        <v>0.42875</v>
       </c>
       <c r="N7" t="n">
-        <v>32.60375</v>
+        <v>32.44875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.48</v>
+        <v>0.515</v>
       </c>
       <c r="N8" t="n">
-        <v>33.04625</v>
+        <v>32.81875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.7737499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>37.14250000000001</v>
+        <v>37.1425</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>119</v>
+      </c>
+      <c r="D75" t="n">
+        <v>80</v>
+      </c>
+      <c r="E75" t="n">
+        <v>39</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.73%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.38125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05238917674150834</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05538020086083217</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
